--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -7525,7 +7525,7 @@
         <v>136704740</v>
       </c>
       <c r="B65" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136704703</v>
       </c>
       <c r="B68" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
